--- a/data/2026/10/pedidos_2026-10-14.xlsx
+++ b/data/2026/10/pedidos_2026-10-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,7 +557,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -627,7 +627,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -696,7 +696,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -765,7 +765,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -834,7 +834,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -903,7 +903,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1389,10 +1389,79 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14. MARY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>73406849</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CHILTIUPAN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>El zonte colonia el espíritu santo chiltiupan</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Casio rosegold diamond</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/2026/10/pedidos_2026-10-14.xlsx
+++ b/data/2026/10/pedidos_2026-10-14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,7 +557,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -627,7 +627,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -696,7 +696,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -765,7 +765,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -834,7 +834,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -903,7 +903,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1389,10 +1389,218 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. René Morales Merka </t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>71461451</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN SALITRILLO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Boulevard Madrid, polígono 19 #25
+Ciudad Real.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Boulevard Madrid</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Merka</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15. Iván Ezequiel Merka</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>69873700</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LISLIQUE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>La Unión, Parque Central de Lislique</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Parque Central de Lislique</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Merka</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16. Isabel de Guzmán</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>61072831</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sonsonate</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ACAJUTLA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>colonia atalaya 2 calle ala achadura</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>galvaniza y gasolinera DLC</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Casio old money rose gold</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
